--- a/template/template_mhs.xlsx
+++ b/template/template_mhs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\rekap_v2\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE271D4-A038-4B4F-B4E7-F9FFB741735A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA12BB3D-3DCF-41CF-9A4B-3DD533E2A78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>NIM</t>
   </si>
@@ -189,6 +189,9 @@
   <si>
     <t>SEMESTER_KELUAR</t>
   </si>
+  <si>
+    <t>BEASISWA</t>
+  </si>
 </sst>
 </file>
 
@@ -337,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -359,6 +362,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BD417"/>
+  <dimension ref="A1:BE417"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
@@ -762,7 +768,7 @@
     <col min="16" max="16" width="13.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
@@ -931,8 +937,11 @@
       <c r="BD1" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE1" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1101,8 +1110,11 @@
       <c r="BD2" s="12">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE2" s="13">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1158,8 +1170,9 @@
       <c r="BB3" s="9"/>
       <c r="BC3" s="11"/>
       <c r="BD3" s="9"/>
-    </row>
-    <row r="4" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE3" s="9"/>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1215,8 +1228,9 @@
       <c r="BB4" s="9"/>
       <c r="BC4" s="11"/>
       <c r="BD4" s="9"/>
-    </row>
-    <row r="5" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE4" s="9"/>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1272,8 +1286,9 @@
       <c r="BB5" s="9"/>
       <c r="BC5" s="11"/>
       <c r="BD5" s="9"/>
-    </row>
-    <row r="6" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE5" s="9"/>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -1329,8 +1344,9 @@
       <c r="BB6" s="9"/>
       <c r="BC6" s="11"/>
       <c r="BD6" s="9"/>
-    </row>
-    <row r="7" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE6" s="9"/>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1386,8 +1402,9 @@
       <c r="BB7" s="9"/>
       <c r="BC7" s="11"/>
       <c r="BD7" s="9"/>
-    </row>
-    <row r="8" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE7" s="9"/>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -1443,8 +1460,9 @@
       <c r="BB8" s="9"/>
       <c r="BC8" s="11"/>
       <c r="BD8" s="9"/>
-    </row>
-    <row r="9" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE8" s="9"/>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1500,8 +1518,9 @@
       <c r="BB9" s="9"/>
       <c r="BC9" s="11"/>
       <c r="BD9" s="9"/>
-    </row>
-    <row r="10" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE9" s="9"/>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1557,8 +1576,9 @@
       <c r="BB10" s="9"/>
       <c r="BC10" s="11"/>
       <c r="BD10" s="9"/>
-    </row>
-    <row r="11" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE10" s="9"/>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -1614,8 +1634,9 @@
       <c r="BB11" s="9"/>
       <c r="BC11" s="11"/>
       <c r="BD11" s="9"/>
-    </row>
-    <row r="12" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE11" s="9"/>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -1671,8 +1692,9 @@
       <c r="BB12" s="9"/>
       <c r="BC12" s="11"/>
       <c r="BD12" s="9"/>
-    </row>
-    <row r="13" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE12" s="9"/>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -1728,8 +1750,9 @@
       <c r="BB13" s="9"/>
       <c r="BC13" s="11"/>
       <c r="BD13" s="9"/>
-    </row>
-    <row r="14" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE13" s="9"/>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -1785,8 +1808,9 @@
       <c r="BB14" s="9"/>
       <c r="BC14" s="11"/>
       <c r="BD14" s="9"/>
-    </row>
-    <row r="15" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE14" s="9"/>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -1842,8 +1866,9 @@
       <c r="BB15" s="9"/>
       <c r="BC15" s="11"/>
       <c r="BD15" s="9"/>
-    </row>
-    <row r="16" spans="1:56" x14ac:dyDescent="0.3">
+      <c r="BE15" s="9"/>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -1899,8 +1924,9 @@
       <c r="BB16" s="9"/>
       <c r="BC16" s="11"/>
       <c r="BD16" s="9"/>
-    </row>
-    <row r="17" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE16" s="9"/>
+    </row>
+    <row r="17" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -1956,8 +1982,9 @@
       <c r="BB17" s="9"/>
       <c r="BC17" s="11"/>
       <c r="BD17" s="9"/>
-    </row>
-    <row r="18" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE17" s="9"/>
+    </row>
+    <row r="18" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2013,8 +2040,9 @@
       <c r="BB18" s="9"/>
       <c r="BC18" s="11"/>
       <c r="BD18" s="9"/>
-    </row>
-    <row r="19" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE18" s="9"/>
+    </row>
+    <row r="19" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2070,8 +2098,9 @@
       <c r="BB19" s="9"/>
       <c r="BC19" s="11"/>
       <c r="BD19" s="9"/>
-    </row>
-    <row r="20" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE19" s="9"/>
+    </row>
+    <row r="20" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -2127,8 +2156,9 @@
       <c r="BB20" s="9"/>
       <c r="BC20" s="11"/>
       <c r="BD20" s="9"/>
-    </row>
-    <row r="21" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE20" s="9"/>
+    </row>
+    <row r="21" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -2184,8 +2214,9 @@
       <c r="BB21" s="9"/>
       <c r="BC21" s="11"/>
       <c r="BD21" s="9"/>
-    </row>
-    <row r="22" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE21" s="9"/>
+    </row>
+    <row r="22" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -2241,8 +2272,9 @@
       <c r="BB22" s="9"/>
       <c r="BC22" s="11"/>
       <c r="BD22" s="9"/>
-    </row>
-    <row r="23" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE22" s="9"/>
+    </row>
+    <row r="23" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -2298,8 +2330,9 @@
       <c r="BB23" s="9"/>
       <c r="BC23" s="11"/>
       <c r="BD23" s="9"/>
-    </row>
-    <row r="24" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE23" s="9"/>
+    </row>
+    <row r="24" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -2355,8 +2388,9 @@
       <c r="BB24" s="9"/>
       <c r="BC24" s="11"/>
       <c r="BD24" s="9"/>
-    </row>
-    <row r="25" spans="2:56" x14ac:dyDescent="0.3">
+      <c r="BE24" s="9"/>
+    </row>
+    <row r="25" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -2374,7 +2408,7 @@
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
     </row>
-    <row r="26" spans="2:56" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -2392,7 +2426,7 @@
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="2:56" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -2410,7 +2444,7 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="2:56" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -2428,7 +2462,7 @@
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="2:56" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -2446,7 +2480,7 @@
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="2:56" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -2464,7 +2498,7 @@
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="2:56" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -2482,7 +2516,7 @@
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="2:56" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:57" x14ac:dyDescent="0.3">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
